--- a/www/download/IND.gdp.s.du.WIOD13.xlsx
+++ b/www/download/IND.gdp.s.du.WIOD13.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>59172.0589864628</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>59715.9080706803</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>59930.7325921164</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>60186.3926719571</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>62577.1940000423</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>66021.3881396857</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>64235.009912061</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>66262.2711616936</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>72799.4638143242</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>81192.9431595083</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>89489.8103686761</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>96647.8335439749</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>112304.938473885</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>134319.057128159</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>131810.804760959</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26993.1999650274</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27103.4411898283</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27069.6449391828</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26910.9848960791</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27340.9534733306</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28555.8429119741</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27796.4084419178</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>28105.3823790047</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30365.2368507588</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33549.1139937556</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>35369.6310782755</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>37004.8727365691</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42083.7094437645</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>47572.4284245116</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>41419.1397864515</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20591.1517595347</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20482.0580133694</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20435.6736495073</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20460.5499682048</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21105.5945557966</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22437.6433531567</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21937.7798269552</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21999.3494574964</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23535.961312143</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25936.9955531466</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27510.8294565259</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29130.3741109324</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33330.3243267202</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>37114.1822426283</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33884.7816910526</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31503.3187718014</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>32181.5989033456</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>30974.8779636796</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29497.7036781035</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28474.2884172852</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>28448.033290584</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26677.5773671646</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27246.3391085926</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29433.9171089611</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33309.1418310874</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>36385.276223579</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>39333.0855349106</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>45494.6741471224</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>49647.4621526117</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>45118.7677630875</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.671</t>
+          <t>671178.509142592</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.658</t>
+          <t>657846.327310356</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.661</t>
+          <t>661402.835689498</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.646</t>
+          <t>645775.891040105</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>686423.130072148</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.719</t>
+          <t>718897.306386656</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.693</t>
+          <t>692787.430156366</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.729</t>
+          <t>729074.729328895</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.794</t>
+          <t>793914.400315939</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.922</t>
+          <t>921737.114727647</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1.002</t>
+          <t>1002136.57914886</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1.049</t>
+          <t>1048722.22749145</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>1204909.00800363</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1369848.54331821</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.257</t>
+          <t>1257107.42233647</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>86001.3264333093</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>87688.5922735156</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>88575.303776634</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>88481.7478671557</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>91671.1615194909</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>97078.4048088399</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>93345.3305798284</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>95926.9130243778</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>104185.496663412</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>117888.04070422</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>126839.43575993</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>134286.195103921</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>154177.731338939</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>171141.681100623</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>155742.600654734</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>7.219</t>
+          <t>7219743.96616262</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7.293</t>
+          <t>7293583.5264036</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>7.274</t>
+          <t>7274826.29700395</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>7.21</t>
+          <t>7210409.12226206</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>7.569</t>
+          <t>7425945.36452055</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7.811</t>
+          <t>7811240.56749132</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7.752</t>
+          <t>7753068.71862439</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>8.111</t>
+          <t>8112415.35776575</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>8.893</t>
+          <t>8893356.07028301</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>9.932</t>
+          <t>9932090.38230274</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>10.672</t>
+          <t>10672609.3733664</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>11.524</t>
+          <t>11524139.9019201</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>13.311</t>
+          <t>13311951.5500386</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>15.159</t>
+          <t>15159148.3148038</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>14.176</t>
+          <t>14176118.0997505</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2050.96203839294</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2038.08169754216</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2011.75227907708</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1997.86414175909</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2045.52610243457</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2133.14894099297</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2089.44688339496</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2135.20238996816</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2379.49268825162</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2666.10781394578</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2870.10480024534</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3043.26953238187</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3503.69015405283</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3813.11196518307</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3600.70193396355</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>49846.1216488528</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50864.3650778949</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>50237.4185401929</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>49024.6496012733</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>48189.8467880837</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>49360.8750256014</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>46180.2291707587</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>46422.4499701225</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>48927.3913113244</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>54117.5722418714</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>58589.2703617767</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>62174.5060422472</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>71453.1260022088</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>80809.6620209815</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>71054.1475589423</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.238</t>
+          <t>237798.160355716</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>231857.88005094</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>227010.275815251</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>226147.996819391</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>228874.291633202</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>236471.243574841</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>226298.240270622</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>226432.400590323</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>239446.987458082</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>264614.139240422</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>279512.471890713</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>292503.569578334</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>0.335</t>
+          <t>334959.616989713</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>370216.475598934</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>0.334</t>
+          <t>333838.556564779</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17377.3600788698</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17366.4938579878</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17571.9142307693</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17856.4989317854</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18357.891325303</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19280.5221830309</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18828.0716859829</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19092.4072637979</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20155.4652736724</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21892.9734285964</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23523.9667635648</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25145.9289697243</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28616.9911635062</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>31838.5225907495</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29226.0796986834</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>93873.5712926095</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>95158.6346667017</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>97969.4982196261</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>101468.365987712</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>108309.903073485</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>118052.991739828</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>117921.38021016</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>123144.191271812</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>134855.839591585</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>151024.242243971</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>165313.474449502</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>177433.662646876</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.203</t>
+          <t>202801.472130149</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>215158.533138026</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>178968.96541712</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6088.87671723142</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5906.94238817744</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5771.48510203149</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5547.81248410525</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5276.1507520347</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5308.13989046519</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5254.12059341404</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5333.81733216831</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6013.76074193333</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6829.42418444583</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7258.15944196673</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8070.10857599595</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9289.79526875552</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10080.0383885284</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7792.56582362023</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17179.7620633131</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17351.4114712142</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17734.8224225007</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17803.3879195042</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18569.2630828975</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19394.884526223</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18784.7722003908</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19150.5585594364</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20367.5067982078</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22477.1995211488</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>24175.1869035318</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25709.7511901932</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29531.750934131</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33065.3928631091</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29142.8679488089</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>137098.68939246</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>137837.213472254</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>135501.298763279</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>134237.214207204</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>138005.53680504</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>141940.857883284</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>138121.124904527</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>137940.235023679</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>147756.668050881</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>165402.05256383</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>177164.80564413</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>186006.580525677</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>215606.008336235</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>241695.59293012</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>217340.045723255</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>164432.690496826</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>165514.765458267</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>165656.054853797</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>164715.105696112</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>166215.672267581</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>171255.184410343</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>166131.56181238</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>168122.325501128</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>179543.656737705</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>197777.106054743</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>213356.487523977</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>223515.060211958</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>252826.704202001</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>276193.934816072</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>252310.487244558</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>35830.6671599677</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>35639.4480147143</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33998.1951541836</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>34533.9999948148</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>36080.9999086362</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>37208.6944243327</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>35766.7609313814</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>35832.3229483028</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>38295.5422935459</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>41592.7460603448</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>44371.8276674773</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>48631.4241772062</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>55151.0860500146</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>59211.8685526236</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>56955.4463617049</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>40555.1226950665</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>40783.6951802624</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>40584.9695934301</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>41094.0054378249</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>42841.6886051572</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>44610.0813773972</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42085.6230153975</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>42998.396067378</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>44899.8135023813</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>48740.7928543724</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50751.8032765386</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>53282.7522114986</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>59859.8635750701</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>62545.9473403813</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>57734.0675396201</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.677</t>
+          <t>676952.012409001</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.686</t>
+          <t>685790.305883517</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.658</t>
+          <t>657852.158584763</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.673</t>
+          <t>672992.649798769</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.761</t>
+          <t>746622.820245945</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.832</t>
+          <t>832517.145328055</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.819</t>
+          <t>819463.282442913</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.877</t>
+          <t>876982.288851177</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.968</t>
+          <t>968459.998229063</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.076</t>
+          <t>1075797.26500864</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1.042</t>
+          <t>1041954.47316191</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1.019</t>
+          <t>1019230.22233258</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.184</t>
+          <t>1184268.76213457</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1.321</t>
+          <t>1321490.43653814</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.253</t>
+          <t>1252779.69494364</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>5.629</t>
+          <t>5629347.29050276</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>5860525.55605773</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>5.866</t>
+          <t>5866697.81206011</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>5.866</t>
+          <t>5866232.92541054</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>6.021</t>
+          <t>5907225.56404746</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6.442</t>
+          <t>6442106.13016309</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>6520327.98589823</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>6521279.65860441</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>7.402</t>
+          <t>7402044.9925138</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>8.363</t>
+          <t>8363281.82277772</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>9.236</t>
+          <t>9236256.05375016</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>9.748</t>
+          <t>9748304.05763111</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>10.699</t>
+          <t>10699740.5240322</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>11.892</t>
+          <t>11892303.0188994</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>11.117</t>
+          <t>11117241.9590451</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11537.5458063279</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12008.3711910982</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12342.3933136236</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12834.3002078146</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13738.3458422826</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14808.8435180132</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14820.3215255166</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15106.2126433601</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16425.3586868055</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18569.3477077424</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20755.2790394425</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>22827.8638830007</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26218.7660346021</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29278.1849674705</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24829.9527076314</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>158816.923238238</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>159576.610393204</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>158736.039653573</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>160292.972888501</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>163154.443159197</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>168030.864970492</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>165093.744233412</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>168567.515049472</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>181167.418220388</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>201077.207892095</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>215132.189744884</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>228740.772344511</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>262139.44905839</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>287915.987070278</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>0.254</t>
+          <t>254491.180592476</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.528</t>
+          <t>528082.714884624</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.531</t>
+          <t>531448.596690732</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0.523</t>
+          <t>523396.037927116</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.498</t>
+          <t>497895.531248571</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.505</t>
+          <t>495472.349439987</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0.513</t>
+          <t>513306.072746691</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.489</t>
+          <t>488825.492766009</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.485</t>
+          <t>485341.592720027</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>0.522</t>
+          <t>521850.474772533</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0.572</t>
+          <t>571779.950323602</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>0.602</t>
+          <t>601657.974582288</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>0.634</t>
+          <t>634381.669643534</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>0.719</t>
+          <t>718866.780851711</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>769762.23995665</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>0.662</t>
+          <t>661679.027577066</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>222807.599441667</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>218213.382737141</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>213427.441321738</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>195129.274730705</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>204732.738345309</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>218895.529216924</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>209682.066917968</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>214853.039849718</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>232565.224135765</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0.266</t>
+          <t>265760.043239129</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>272933.312637219</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>285063.076008834</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>314597.533264145</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>350420.007798331</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>0.326</t>
+          <t>325882.621906374</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13578.5262651539</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13751.7981651506</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13240.0144294497</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13839.087686781</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13313.5527232972</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14100.3312951865</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13069.2232914911</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13400.2581191762</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14760.6972895174</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16061.1037998464</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18111.8750152956</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18588.6779752404</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21676.3284967425</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23256.6255317423</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19847.5550245062</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1230.65844310583</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1268.62325078242</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1294.52380571379</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1315.85189346228</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1340.39238939926</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1472.17781652611</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1481.11259033533</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1569.4368443911</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1818.74813366172</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2054.24680316776</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2252.29798792414</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2420.76653743076</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2823.62880223353</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3364.6605568655</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3157.58638702789</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7368.90415598645</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7271.44457518326</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7460.46278053202</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7245.75860104616</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6954.85535327867</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6556.95026181654</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6243.90372930199</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6238.734490976</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6886.695976349</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7572.98755198099</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8269.00073040533</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8981.66593584503</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10366.3949657856</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10984.2142650211</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7510.82657979326</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>336762.818274784</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>353901.361923456</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>356543.5866438</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>365040.816922234</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.391</t>
+          <t>383973.014321473</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.408</t>
+          <t>408417.015401615</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.399</t>
+          <t>399293.67435712</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>409792.5958336</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.455</t>
+          <t>455428.385085813</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.523</t>
+          <t>523275.411380457</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.559</t>
+          <t>559113.821545976</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.594</t>
+          <t>594121.936245869</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.674</t>
+          <t>673845.447542984</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.807</t>
+          <t>806544.539153976</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.737</t>
+          <t>737361.965955802</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1023.9796317015</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1036.15226171218</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1033.6015456093</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1042.19639611116</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1079.23020027375</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1135.57966917236</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>953.385379299043</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1150.37051621626</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1146.19427549197</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1267.71302832736</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1328.96596846584</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1405.02712773466</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1586.82081268657</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1672.36250814249</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1533.26365293706</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>37572.2270324727</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>38262.4417043157</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>38870.8125448754</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>38730.0406924976</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>40378.049492102</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>42967.4718002669</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42337.3327210818</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>43441.1799137155</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>46546.0989691137</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50582.3276416073</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>53833.7177714167</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>56753.4937059815</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>64904.0925136771</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>73450.4846601281</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>68025.8556899876</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>160804.043113452</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>164555.914026334</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>164534.72915838</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>162601.986044795</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>160041.432680099</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>163448.612009495</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>138899.964399731</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>135049.547437497</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>142781.203715399</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>157871.389904162</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>171180.44976532</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>182732.470178821</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>211275.290974704</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>242985.634382341</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>218635.627279594</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>39544.327237294</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>39995.3861980847</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>39795.2970784847</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>39849.2836259074</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>41167.7187865514</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>43914.9557806208</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>42664.0131423747</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>43583.2791705226</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>45598.0877678798</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>49762.4016145392</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>52193.1665915941</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>54957.706899866</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>61899.0795384473</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>67487.7069077418</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>60795.6348088978</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>109146.706415406</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>112357.927107829</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>105756.416381103</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>101531.579344478</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>127152.155964851</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>130436.14724932</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>125358.862329208</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>112120.930787506</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>118776.931598696</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>123536.084752247</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>130627.959241923</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>136961.60947592</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>155420.946553022</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>172158.362706065</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>156031.835939284</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0.863</t>
+          <t>863156.853326213</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0.845</t>
+          <t>845252.721501526</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.802</t>
+          <t>801720.721015889</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.756</t>
+          <t>756438.011134455</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.788</t>
+          <t>773309.227419471</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.811</t>
+          <t>811011.26286213</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.786</t>
+          <t>786338.901524814</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.798</t>
+          <t>797862.505569768</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0.855</t>
+          <t>855174.338003174</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>939950.349325188</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1000047.69637201</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>1.049</t>
+          <t>1049073.83969758</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>1.193</t>
+          <t>1193141.81601563</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>1.316</t>
+          <t>1316241.29993824</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>1.186</t>
+          <t>1185812.78944369</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20182.7053736059</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19859.2759203141</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19372.6400529425</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18592.7758177843</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18095.0742126066</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18227.4180987544</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17426.3380887609</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16934.0181724517</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17779.7361656655</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20073.6210357521</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>21415.6452100576</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22133.5548535442</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25919.9161659021</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30047.0083643439</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26847.1605018169</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9125.71179491985</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8815.79849729716</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8573.6918538254</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8400.88851834827</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8549.29053669251</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8877.49410398171</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8599.81083072856</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8674.91652359308</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9200.07742434916</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10049.7498637467</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10718.8342540742</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11242.3370763654</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12963.7671429455</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15075.5189841744</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13312.8661901505</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>30532.5953008492</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>30612.4608258676</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29956.4045921361</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30186.0890697162</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>31463.0669893562</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32978.3890353431</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>32396.3108812915</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32802.4979215489</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>34767.4418878247</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>38463.506464647</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>41040.4663177978</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>43003.9713255527</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>50240.6965496213</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>56293.3786549201</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50915.4267663781</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>249227.200149191</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>261190.702635552</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.259</t>
+          <t>258904.296908546</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>247505.731188617</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>250485.847494515</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>240439.536769983</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>233948.808753528</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>229883.375519939</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>240888.054129573</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>270293.611663851</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>286504.984610588</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>285845.552332451</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>302572.058417624</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>341132.329567782</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>0.313</t>
+          <t>312536.269429478</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>98088.6868813583</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>96494.0587863768</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>97426.6898778381</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>95265.2314364554</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>96226.3070563425</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>100726.373023573</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>90399.4942877335</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>92147.9273567074</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>100004.387920279</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>112812.437255157</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>122545.064226523</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>129465.615907595</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>149526.460459952</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>166127.043583435</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>145372.490890363</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>0.729</t>
+          <t>729101.842603441</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>0.744</t>
+          <t>743571.814825787</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.756</t>
+          <t>756063.114105575</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0.765</t>
+          <t>765192.192890281</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0.806</t>
+          <t>790333.23754016</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>0.841</t>
+          <t>841055.712527798</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.804</t>
+          <t>803664.402927172</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.803</t>
+          <t>803003.751375213</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>0.856</t>
+          <t>856291.989701713</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0.956</t>
+          <t>956009.255838614</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>1.033</t>
+          <t>1033247.89214541</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>1.111</t>
+          <t>1110558.21968627</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>1.255</t>
+          <t>1255198.62890625</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>1.363</t>
+          <t>1362799.36615195</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>1.193</t>
+          <t>1193142.9862503</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>10.503</t>
+          <t>10503849.2444567</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>10.799</t>
+          <t>10799916.5128</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>10.908</t>
+          <t>10908823.4723415</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>11.001</t>
+          <t>11001270.4165663</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>11.644</t>
+          <t>11422878.609273</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>12.359</t>
+          <t>12359380.993308</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>12.428</t>
+          <t>12429849.4254215</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>13.114</t>
+          <t>13116096.8190777</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>14.722</t>
+          <t>14723335.2227697</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>16.696</t>
+          <t>16696100.0668836</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>18.261</t>
+          <t>18262174.0514356</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>19.862</t>
+          <t>19862057.6184677</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>22.684</t>
+          <t>22686355.612386</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>25.879</t>
+          <t>25879752.7879427</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>24.445</t>
+          <t>24445465.03624</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>29.352</t>
+          <t>29355156.6318989</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>29.983</t>
+          <t>29984597.6014596</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>29.997</t>
+          <t>29999085.4085658</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>29.936</t>
+          <t>29935574.8857193</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>30853991.7804162</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>33.031</t>
+          <t>33032506.8173154</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>32.884</t>
+          <t>32888447.4450266</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>34.048</t>
+          <t>34053517.1014926</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>37.821</t>
+          <t>37823930.4281687</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>42.594</t>
+          <t>42594839.9902356</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>46.198</t>
+          <t>46200523.666232</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>49.524</t>
+          <t>49523632.8293773</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>56.248</t>
+          <t>56253400.8421983</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>63.571</t>
+          <t>63573963.9484651</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>59.362</t>
+          <t>59362375.1623606</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>gdp.s.du</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD13</t>
